--- a/03-price-monitor/output/price_report.xlsx
+++ b/03-price-monitor/output/price_report.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Latest Prices'!$A$1:$H$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alerts'!$A$1:$E$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'History'!$A$1:$E$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'History'!$A$1:$E$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,11 +493,11 @@
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-27T15:21:00+00:00</t>
+          <t>2026-10-27T15:42:01+00:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -525,11 +525,11 @@
         <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-27T15:21:00+00:00</t>
+          <t>2026-10-27T15:42:01+00:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -557,11 +557,11 @@
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-27T15:21:00+00:00</t>
+          <t>2026-10-27T15:42:01+00:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -589,11 +589,11 @@
         <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-27T15:21:00+00:00</t>
+          <t>2026-10-27T15:42:01+00:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -621,11 +621,11 @@
         <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-27T15:21:00+00:00</t>
+          <t>2026-10-27T15:42:01+00:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -653,11 +653,11 @@
         <v>9</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-27T15:21:00+00:00</t>
+          <t>2026-10-27T15:42:01+00:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -685,11 +685,11 @@
         <v>12</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-10-27T15:21:00+00:00</t>
+          <t>2026-10-27T15:42:01+00:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -750,7 +750,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27T15:21:00+00:00</t>
+          <t>2026-10-27T15:42:01+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -777,7 +777,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-27T15:21:00+00:00</t>
+          <t>2026-10-27T15:42:01+00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -804,7 +804,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27T15:21:00+00:00</t>
+          <t>2026-10-27T15:42:01+00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-27T15:21:00+00:00</t>
+          <t>2026-10-27T15:42:01+00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -858,7 +858,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-27T15:21:00+00:00</t>
+          <t>2026-10-27T15:42:01+00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-27T15:21:00+00:00</t>
+          <t>2026-10-27T15:42:01+00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-27T15:21:00+00:00</t>
+          <t>2026-10-27T15:42:01+00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -948,7 +948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1307,8 +1307,169 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-27T15:42:01+00:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>We Are All Completely Beside Ourselves</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>24.04</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/we-are-all-completely-beside-ourselves_301/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-27T15:42:01+00:00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>The Rise of Theodore Roosevelt (Theodore Roosevelt #1)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>42.57</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-rise-of-theodore-roosevelt-theodore-roosevelt-1_276/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-27T15:42:01+00:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>44.88</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/rework_212/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-27T15:42:01+00:00</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dark Notes</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>19.19</v>
+      </c>
+      <c r="D19" t="n">
+        <v>15</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/dark-notes_800/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-27T15:42:01+00:00</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>The Art and Science of Low Carbohydrate Living</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>52.98</v>
+      </c>
+      <c r="D20" t="n">
+        <v>9</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-art-and-science-of-low-carbohydrate-living_570/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-27T15:42:01+00:00</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Suzie Snowflake: One beautiful flake (a self-esteem story)</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="D21" t="n">
+        <v>9</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/suzie-snowflake-one-beautiful-flake-a-self-esteem-story_568/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-27T15:42:01+00:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Equal Is Unfair: America's Misguided Fight Against Income Inequality</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>56.86</v>
+      </c>
+      <c r="D22" t="n">
+        <v>12</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/equal-is-unfair-americas-misguided-fight-against-income-inequality_617/index.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E15"/>
+  <autoFilter ref="A1:E22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>